--- a/Palmares/fichier excel/aggregats_ecoles_EQUATEUR12022.xlsx
+++ b/Palmares/fichier excel/aggregats_ecoles_EQUATEUR12022.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6420ee82958214d8/Documents/GitHub/Projet-tutore/Palmares/fichier excel/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_EAE10028AE611DFFC79B6F807FCDD5408A00AAA9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Écoles" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -2758,8 +2764,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2796,34 +2802,42 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AggregatsEcoles" displayName="AggregatsEcoles" ref="A1:L540" totalsRowShown="0">
-  <autoFilter ref="A1:L540"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AggregatsEcoles" displayName="AggregatsEcoles" ref="A1:L540" totalsRowShown="0">
+  <autoFilter ref="A1:L540" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" name="CodeEcole"/>
-    <tableColumn id="2" name="Ecole"/>
-    <tableColumn id="3" name="ProvinceEduc"/>
-    <tableColumn id="4" name="Annee"/>
-    <tableColumn id="5" name="CodeOption"/>
-    <tableColumn id="6" name="Option"/>
-    <tableColumn id="7" name="PartTot"/>
-    <tableColumn id="8" name="PartH"/>
-    <tableColumn id="9" name="PartF"/>
-    <tableColumn id="10" name="ReussTot"/>
-    <tableColumn id="11" name="ReussH"/>
-    <tableColumn id="12" name="ReussF"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="CodeEcole"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Ecole"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ProvinceEduc"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Annee"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="CodeOption"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Option"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PartTot"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="PartH"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="PartF"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="ReussTot"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="ReussH"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="ReussF"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2861,7 +2875,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2895,6 +2909,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2929,9 +2944,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3104,23 +3120,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L540"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="12" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>901</v>
       </c>
@@ -3158,7 +3174,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3196,7 +3212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3234,7 +3250,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -3269,7 +3285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3304,7 +3320,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -3339,7 +3355,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3377,7 +3393,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3415,7 +3431,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -3453,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3488,7 +3504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3523,7 +3539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3558,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -3596,7 +3612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -3634,7 +3650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3672,7 +3688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -3710,7 +3726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -3748,7 +3764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -3786,7 +3802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -3824,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -3862,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -3897,7 +3913,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -3935,7 +3951,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -3973,7 +3989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -4008,7 +4024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -4046,7 +4062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -4084,7 +4100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -4122,7 +4138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -4157,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -4192,7 +4208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -4227,7 +4243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -4262,7 +4278,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -4300,7 +4316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -4338,7 +4354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -4376,7 +4392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -4414,7 +4430,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -4452,7 +4468,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -4487,7 +4503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -4522,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -4557,7 +4573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -4592,7 +4608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -4627,7 +4643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -4665,7 +4681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -4700,7 +4716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -4738,7 +4754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -4776,7 +4792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -4814,7 +4830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -4852,7 +4868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -4887,7 +4903,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -4922,7 +4938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -4960,7 +4976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -4998,7 +5014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -5033,7 +5049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -5068,7 +5084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -5103,7 +5119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -5138,7 +5154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -5176,7 +5192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -5214,7 +5230,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -5252,7 +5268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -5287,7 +5303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -5322,7 +5338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -5357,7 +5373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -5395,7 +5411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -5433,7 +5449,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -5468,7 +5484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -5503,7 +5519,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -5538,7 +5554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -5573,7 +5589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -5611,7 +5627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -5649,7 +5665,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -5687,7 +5703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -5725,7 +5741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>70</v>
       </c>
@@ -5760,7 +5776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -5798,7 +5814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -5836,7 +5852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -5871,7 +5887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>74</v>
       </c>
@@ -5906,7 +5922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>75</v>
       </c>
@@ -5941,7 +5957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -5976,7 +5992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>77</v>
       </c>
@@ -6014,7 +6030,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -6052,7 +6068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>79</v>
       </c>
@@ -6090,7 +6106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>80</v>
       </c>
@@ -6128,7 +6144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>81</v>
       </c>
@@ -6166,7 +6182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>82</v>
       </c>
@@ -6201,7 +6217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -6239,7 +6255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>84</v>
       </c>
@@ -6277,7 +6293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>85</v>
       </c>
@@ -6315,7 +6331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>86</v>
       </c>
@@ -6353,7 +6369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>87</v>
       </c>
@@ -6391,7 +6407,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>88</v>
       </c>
@@ -6429,7 +6445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>89</v>
       </c>
@@ -6464,7 +6480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>90</v>
       </c>
@@ -6499,7 +6515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>91</v>
       </c>
@@ -6537,7 +6553,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>92</v>
       </c>
@@ -6572,7 +6588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>93</v>
       </c>
@@ -6610,7 +6626,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -6645,7 +6661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>95</v>
       </c>
@@ -6683,7 +6699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>96</v>
       </c>
@@ -6721,7 +6737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>97</v>
       </c>
@@ -6759,7 +6775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>98</v>
       </c>
@@ -6797,7 +6813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -6835,7 +6851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>100</v>
       </c>
@@ -6873,7 +6889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>101</v>
       </c>
@@ -6908,7 +6924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>102</v>
       </c>
@@ -6943,7 +6959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -6981,7 +6997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>104</v>
       </c>
@@ -7019,7 +7035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>105</v>
       </c>
@@ -7057,7 +7073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>106</v>
       </c>
@@ -7095,7 +7111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -7133,7 +7149,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -7171,7 +7187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -7209,7 +7225,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>110</v>
       </c>
@@ -7244,7 +7260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>111</v>
       </c>
@@ -7279,7 +7295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>112</v>
       </c>
@@ -7317,7 +7333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>113</v>
       </c>
@@ -7355,7 +7371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -7393,7 +7409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -7428,7 +7444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>116</v>
       </c>
@@ -7463,7 +7479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>117</v>
       </c>
@@ -7501,7 +7517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>118</v>
       </c>
@@ -7539,7 +7555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>119</v>
       </c>
@@ -7577,7 +7593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>120</v>
       </c>
@@ -7615,7 +7631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>121</v>
       </c>
@@ -7653,7 +7669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>122</v>
       </c>
@@ -7691,7 +7707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>123</v>
       </c>
@@ -7726,7 +7742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>124</v>
       </c>
@@ -7761,7 +7777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>125</v>
       </c>
@@ -7796,7 +7812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>126</v>
       </c>
@@ -7834,7 +7850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>127</v>
       </c>
@@ -7872,7 +7888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>128</v>
       </c>
@@ -7910,7 +7926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>129</v>
       </c>
@@ -7948,7 +7964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:12">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>130</v>
       </c>
@@ -7986,7 +8002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:12">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>131</v>
       </c>
@@ -8024,7 +8040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>132</v>
       </c>
@@ -8062,7 +8078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:12">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>133</v>
       </c>
@@ -8100,7 +8116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:12">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>134</v>
       </c>
@@ -8138,7 +8154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -8173,7 +8189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>136</v>
       </c>
@@ -8208,7 +8224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:12">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>137</v>
       </c>
@@ -8246,7 +8262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>138</v>
       </c>
@@ -8281,7 +8297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:12">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>139</v>
       </c>
@@ -8319,7 +8335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>140</v>
       </c>
@@ -8357,7 +8373,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>141</v>
       </c>
@@ -8395,7 +8411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>142</v>
       </c>
@@ -8433,7 +8449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>143</v>
       </c>
@@ -8471,7 +8487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:12">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>144</v>
       </c>
@@ -8509,7 +8525,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:12">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>145</v>
       </c>
@@ -8547,7 +8563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:12">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>146</v>
       </c>
@@ -8582,7 +8598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:12">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>147</v>
       </c>
@@ -8620,7 +8636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:12">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>148</v>
       </c>
@@ -8658,7 +8674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:12">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>149</v>
       </c>
@@ -8696,7 +8712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>150</v>
       </c>
@@ -8734,7 +8750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:12">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>151</v>
       </c>
@@ -8772,7 +8788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="154" spans="1:12">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>152</v>
       </c>
@@ -8810,7 +8826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:12">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>153</v>
       </c>
@@ -8845,7 +8861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>154</v>
       </c>
@@ -8883,7 +8899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:12">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>155</v>
       </c>
@@ -8918,7 +8934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:12">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>156</v>
       </c>
@@ -8953,7 +8969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:12">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>157</v>
       </c>
@@ -8991,7 +9007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:12">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>158</v>
       </c>
@@ -9029,7 +9045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:12">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>159</v>
       </c>
@@ -9067,7 +9083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:12">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>160</v>
       </c>
@@ -9105,7 +9121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>161</v>
       </c>
@@ -9143,7 +9159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:12">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>162</v>
       </c>
@@ -9181,7 +9197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:12">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>163</v>
       </c>
@@ -9219,7 +9235,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:12">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>164</v>
       </c>
@@ -9257,7 +9273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:12">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>165</v>
       </c>
@@ -9292,7 +9308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:12">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>166</v>
       </c>
@@ -9327,7 +9343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:12">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>167</v>
       </c>
@@ -9365,7 +9381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:12">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>168</v>
       </c>
@@ -9403,7 +9419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:12">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>169</v>
       </c>
@@ -9438,7 +9454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:12">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>170</v>
       </c>
@@ -9476,7 +9492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:12">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>171</v>
       </c>
@@ -9514,7 +9530,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:12">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>172</v>
       </c>
@@ -9552,7 +9568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:12">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>173</v>
       </c>
@@ -9590,7 +9606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:12">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>174</v>
       </c>
@@ -9628,7 +9644,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:12">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>175</v>
       </c>
@@ -9666,7 +9682,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:12">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>176</v>
       </c>
@@ -9704,7 +9720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:12">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>177</v>
       </c>
@@ -9742,7 +9758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:12">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>178</v>
       </c>
@@ -9777,7 +9793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:12">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>179</v>
       </c>
@@ -9815,7 +9831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:12">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>180</v>
       </c>
@@ -9850,7 +9866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:12">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>181</v>
       </c>
@@ -9888,7 +9904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:12">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>182</v>
       </c>
@@ -9926,7 +9942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="185" spans="1:12">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>183</v>
       </c>
@@ -9964,7 +9980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:12">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>184</v>
       </c>
@@ -10002,7 +10018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:12">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>185</v>
       </c>
@@ -10040,7 +10056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:12">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>186</v>
       </c>
@@ -10075,7 +10091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:12">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>187</v>
       </c>
@@ -10113,7 +10129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:12">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>188</v>
       </c>
@@ -10151,7 +10167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:12">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>189</v>
       </c>
@@ -10186,7 +10202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:12">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>190</v>
       </c>
@@ -10221,7 +10237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" spans="1:12">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>191</v>
       </c>
@@ -10259,7 +10275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:12">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>192</v>
       </c>
@@ -10297,7 +10313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:12">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>193</v>
       </c>
@@ -10335,7 +10351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:12">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>194</v>
       </c>
@@ -10373,7 +10389,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:12">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>195</v>
       </c>
@@ -10411,7 +10427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:12">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>196</v>
       </c>
@@ -10449,7 +10465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:12">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>197</v>
       </c>
@@ -10487,7 +10503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:12">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>198</v>
       </c>
@@ -10525,7 +10541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:12">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -10560,7 +10576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:12">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>200</v>
       </c>
@@ -10595,7 +10611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:12">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>201</v>
       </c>
@@ -10633,7 +10649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:12">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>202</v>
       </c>
@@ -10671,7 +10687,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:12">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>203</v>
       </c>
@@ -10709,7 +10725,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="206" spans="1:12">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>204</v>
       </c>
@@ -10747,7 +10763,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:12">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>205</v>
       </c>
@@ -10785,7 +10801,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:12">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>206</v>
       </c>
@@ -10823,7 +10839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:12">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>207</v>
       </c>
@@ -10858,7 +10874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:12">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>208</v>
       </c>
@@ -10893,7 +10909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:12">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>209</v>
       </c>
@@ -10928,7 +10944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:12">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>210</v>
       </c>
@@ -10963,7 +10979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="213" spans="1:12">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>211</v>
       </c>
@@ -10998,7 +11014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:12">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>212</v>
       </c>
@@ -11036,7 +11052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:12">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>213</v>
       </c>
@@ -11074,7 +11090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:12">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>214</v>
       </c>
@@ -11112,7 +11128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="217" spans="1:12">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>215</v>
       </c>
@@ -11150,7 +11166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:12">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>216</v>
       </c>
@@ -11188,7 +11204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:12">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>217</v>
       </c>
@@ -11226,7 +11242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:12">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>218</v>
       </c>
@@ -11264,7 +11280,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="221" spans="1:12">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>219</v>
       </c>
@@ -11299,7 +11315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:12">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>220</v>
       </c>
@@ -11337,7 +11353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:12">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>221</v>
       </c>
@@ -11375,7 +11391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:12">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>222</v>
       </c>
@@ -11413,7 +11429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:12">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>223</v>
       </c>
@@ -11451,7 +11467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:12">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>224</v>
       </c>
@@ -11489,7 +11505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:12">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>225</v>
       </c>
@@ -11527,7 +11543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:12">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>226</v>
       </c>
@@ -11565,7 +11581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:12">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>227</v>
       </c>
@@ -11603,7 +11619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:12">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>228</v>
       </c>
@@ -11641,7 +11657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:12">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>229</v>
       </c>
@@ -11679,7 +11695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:12">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>230</v>
       </c>
@@ -11717,7 +11733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:12">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>231</v>
       </c>
@@ -11755,7 +11771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:12">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>232</v>
       </c>
@@ -11793,7 +11809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:12">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>233</v>
       </c>
@@ -11828,7 +11844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:12">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>234</v>
       </c>
@@ -11863,7 +11879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:12">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>235</v>
       </c>
@@ -11898,7 +11914,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="238" spans="1:12">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>236</v>
       </c>
@@ -11933,7 +11949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:12">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>237</v>
       </c>
@@ -11971,7 +11987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:12">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>238</v>
       </c>
@@ -12006,7 +12022,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:12">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>239</v>
       </c>
@@ -12044,7 +12060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:12">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>240</v>
       </c>
@@ -12082,7 +12098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:12">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>241</v>
       </c>
@@ -12120,7 +12136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:12">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>242</v>
       </c>
@@ -12158,7 +12174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:12">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>243</v>
       </c>
@@ -12196,7 +12212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246" spans="1:12">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>244</v>
       </c>
@@ -12234,7 +12250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="247" spans="1:12">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>245</v>
       </c>
@@ -12272,7 +12288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:12">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>246</v>
       </c>
@@ -12310,7 +12326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:12">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>247</v>
       </c>
@@ -12348,7 +12364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="1:12">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>248</v>
       </c>
@@ -12383,7 +12399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:12">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>249</v>
       </c>
@@ -12418,7 +12434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:12">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>250</v>
       </c>
@@ -12456,7 +12472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:12">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>251</v>
       </c>
@@ -12491,7 +12507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:12">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>252</v>
       </c>
@@ -12526,7 +12542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="1:12">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>253</v>
       </c>
@@ -12564,7 +12580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:12">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>254</v>
       </c>
@@ -12599,7 +12615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:12">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>255</v>
       </c>
@@ -12637,7 +12653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:12">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>256</v>
       </c>
@@ -12675,7 +12691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:12">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>257</v>
       </c>
@@ -12713,7 +12729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:12">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>258</v>
       </c>
@@ -12751,7 +12767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:12">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>259</v>
       </c>
@@ -12789,7 +12805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:12">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>260</v>
       </c>
@@ -12827,7 +12843,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="263" spans="1:12">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>261</v>
       </c>
@@ -12865,7 +12881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:12">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>262</v>
       </c>
@@ -12900,7 +12916,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="265" spans="1:12">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>263</v>
       </c>
@@ -12938,7 +12954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:12">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>264</v>
       </c>
@@ -12973,7 +12989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:12">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>265</v>
       </c>
@@ -13011,7 +13027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:12">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>266</v>
       </c>
@@ -13049,7 +13065,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:12">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>267</v>
       </c>
@@ -13087,7 +13103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:12">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>268</v>
       </c>
@@ -13125,7 +13141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:12">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>269</v>
       </c>
@@ -13163,7 +13179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:12">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>270</v>
       </c>
@@ -13201,7 +13217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:12">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>271</v>
       </c>
@@ -13239,7 +13255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:12">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>272</v>
       </c>
@@ -13277,7 +13293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:12">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>273</v>
       </c>
@@ -13315,7 +13331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:12">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>274</v>
       </c>
@@ -13353,7 +13369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:12">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>275</v>
       </c>
@@ -13391,7 +13407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:12">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>276</v>
       </c>
@@ -13429,7 +13445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:12">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>277</v>
       </c>
@@ -13467,7 +13483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" spans="1:12">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>278</v>
       </c>
@@ -13505,7 +13521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="281" spans="1:12">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>279</v>
       </c>
@@ -13540,7 +13556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:12">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>280</v>
       </c>
@@ -13578,7 +13594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:12">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>281</v>
       </c>
@@ -13616,7 +13632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="1:12">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>282</v>
       </c>
@@ -13654,7 +13670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:12">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>283</v>
       </c>
@@ -13692,7 +13708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:12">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>284</v>
       </c>
@@ -13730,7 +13746,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="287" spans="1:12">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>285</v>
       </c>
@@ -13768,7 +13784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:12">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>286</v>
       </c>
@@ -13803,7 +13819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:12">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>287</v>
       </c>
@@ -13838,7 +13854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:12">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>288</v>
       </c>
@@ -13876,7 +13892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:12">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>289</v>
       </c>
@@ -13914,7 +13930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:12">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>290</v>
       </c>
@@ -13952,7 +13968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:12">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>291</v>
       </c>
@@ -13990,7 +14006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:12">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>292</v>
       </c>
@@ -14028,7 +14044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:12">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>293</v>
       </c>
@@ -14066,7 +14082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:12">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>294</v>
       </c>
@@ -14104,7 +14120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:12">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>295</v>
       </c>
@@ -14142,7 +14158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="298" spans="1:12">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>296</v>
       </c>
@@ -14180,7 +14196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:12">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>297</v>
       </c>
@@ -14218,7 +14234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:12">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>298</v>
       </c>
@@ -14256,7 +14272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:12">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>299</v>
       </c>
@@ -14294,7 +14310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:12">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>300</v>
       </c>
@@ -14332,7 +14348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:12">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>301</v>
       </c>
@@ -14367,7 +14383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:12">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>302</v>
       </c>
@@ -14402,7 +14418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:12">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>303</v>
       </c>
@@ -14440,7 +14456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:12">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>304</v>
       </c>
@@ -14478,7 +14494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:12">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>305</v>
       </c>
@@ -14516,7 +14532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:12">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>306</v>
       </c>
@@ -14551,7 +14567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:12">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>307</v>
       </c>
@@ -14586,7 +14602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:12">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>308</v>
       </c>
@@ -14624,7 +14640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:12">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>309</v>
       </c>
@@ -14662,7 +14678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:12">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>310</v>
       </c>
@@ -14700,7 +14716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:12">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>311</v>
       </c>
@@ -14738,7 +14754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:12">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>312</v>
       </c>
@@ -14776,7 +14792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:12">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>313</v>
       </c>
@@ -14814,7 +14830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:12">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>314</v>
       </c>
@@ -14852,7 +14868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:12">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>315</v>
       </c>
@@ -14890,7 +14906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:12">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>316</v>
       </c>
@@ -14928,7 +14944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:12">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>317</v>
       </c>
@@ -14966,7 +14982,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="320" spans="1:12">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>318</v>
       </c>
@@ -15001,7 +15017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:12">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>319</v>
       </c>
@@ -15036,7 +15052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:12">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>320</v>
       </c>
@@ -15071,7 +15087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:12">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>321</v>
       </c>
@@ -15109,7 +15125,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:12">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>322</v>
       </c>
@@ -15147,7 +15163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:12">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>323</v>
       </c>
@@ -15185,7 +15201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:12">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>324</v>
       </c>
@@ -15223,7 +15239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:12">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>325</v>
       </c>
@@ -15261,7 +15277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:12">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>326</v>
       </c>
@@ -15299,7 +15315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:12">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>327</v>
       </c>
@@ -15334,7 +15350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:12">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>328</v>
       </c>
@@ -15369,7 +15385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:12">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>329</v>
       </c>
@@ -15404,7 +15420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:12">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>330</v>
       </c>
@@ -15442,7 +15458,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="333" spans="1:12">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>331</v>
       </c>
@@ -15480,7 +15496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:12">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>332</v>
       </c>
@@ -15518,7 +15534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="335" spans="1:12">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>333</v>
       </c>
@@ -15556,7 +15572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:12">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>334</v>
       </c>
@@ -15591,7 +15607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:12">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>335</v>
       </c>
@@ -15629,7 +15645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:12">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>336</v>
       </c>
@@ -15667,7 +15683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:12">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>337</v>
       </c>
@@ -15705,7 +15721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:12">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>338</v>
       </c>
@@ -15743,7 +15759,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="341" spans="1:12">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>339</v>
       </c>
@@ -15781,7 +15797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:12">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>340</v>
       </c>
@@ -15819,7 +15835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="343" spans="1:12">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>341</v>
       </c>
@@ -15857,7 +15873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:12">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>342</v>
       </c>
@@ -15895,7 +15911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="345" spans="1:12">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>343</v>
       </c>
@@ -15930,7 +15946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:12">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>344</v>
       </c>
@@ -15968,7 +15984,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="347" spans="1:12">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>345</v>
       </c>
@@ -16006,7 +16022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="1:12">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>346</v>
       </c>
@@ -16044,7 +16060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="349" spans="1:12">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>347</v>
       </c>
@@ -16082,7 +16098,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="350" spans="1:12">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>348</v>
       </c>
@@ -16120,7 +16136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:12">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>349</v>
       </c>
@@ -16155,7 +16171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:12">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>350</v>
       </c>
@@ -16190,7 +16206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:12">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>351</v>
       </c>
@@ -16225,7 +16241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:12">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>352</v>
       </c>
@@ -16263,7 +16279,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="355" spans="1:12">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>353</v>
       </c>
@@ -16301,7 +16317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:12">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>354</v>
       </c>
@@ -16339,7 +16355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="357" spans="1:12">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>355</v>
       </c>
@@ -16377,7 +16393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:12">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>356</v>
       </c>
@@ -16415,7 +16431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:12">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>357</v>
       </c>
@@ -16453,7 +16469,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="360" spans="1:12">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>358</v>
       </c>
@@ -16491,7 +16507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="361" spans="1:12">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>359</v>
       </c>
@@ -16529,7 +16545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:12">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>360</v>
       </c>
@@ -16564,7 +16580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:12">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>361</v>
       </c>
@@ -16599,7 +16615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:12">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>362</v>
       </c>
@@ -16634,7 +16650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:12">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>363</v>
       </c>
@@ -16672,7 +16688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366" spans="1:12">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>364</v>
       </c>
@@ -16710,7 +16726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="367" spans="1:12">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>365</v>
       </c>
@@ -16745,7 +16761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:12">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>366</v>
       </c>
@@ -16783,7 +16799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="369" spans="1:12">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>367</v>
       </c>
@@ -16821,7 +16837,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="370" spans="1:12">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>368</v>
       </c>
@@ -16859,7 +16875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:12">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>369</v>
       </c>
@@ -16897,7 +16913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="372" spans="1:12">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>370</v>
       </c>
@@ -16932,7 +16948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:12">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>371</v>
       </c>
@@ -16967,7 +16983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:12">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>372</v>
       </c>
@@ -17002,7 +17018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:12">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>373</v>
       </c>
@@ -17040,7 +17056,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="376" spans="1:12">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>374</v>
       </c>
@@ -17078,7 +17094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:12">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>375</v>
       </c>
@@ -17116,7 +17132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:12">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>376</v>
       </c>
@@ -17154,7 +17170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:12">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>377</v>
       </c>
@@ -17192,7 +17208,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="380" spans="1:12">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>378</v>
       </c>
@@ -17230,7 +17246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:12">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>379</v>
       </c>
@@ -17265,7 +17281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:12">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>380</v>
       </c>
@@ -17300,7 +17316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="383" spans="1:12">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>381</v>
       </c>
@@ -17338,7 +17354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:12">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>382</v>
       </c>
@@ -17376,7 +17392,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" spans="1:12">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>383</v>
       </c>
@@ -17414,7 +17430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:12">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>384</v>
       </c>
@@ -17452,7 +17468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="387" spans="1:12">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>385</v>
       </c>
@@ -17490,7 +17506,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="388" spans="1:12">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>386</v>
       </c>
@@ -17525,7 +17541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:12">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>387</v>
       </c>
@@ -17563,7 +17579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:12">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>388</v>
       </c>
@@ -17601,7 +17617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:12">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>389</v>
       </c>
@@ -17639,7 +17655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="392" spans="1:12">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>390</v>
       </c>
@@ -17677,7 +17693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="393" spans="1:12">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>391</v>
       </c>
@@ -17715,7 +17731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="394" spans="1:12">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>392</v>
       </c>
@@ -17750,7 +17766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:12">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>393</v>
       </c>
@@ -17785,7 +17801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:12">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>394</v>
       </c>
@@ -17820,7 +17836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:12">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>395</v>
       </c>
@@ -17855,7 +17871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:12">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>396</v>
       </c>
@@ -17890,7 +17906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:12">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>397</v>
       </c>
@@ -17925,7 +17941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:12">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>398</v>
       </c>
@@ -17960,7 +17976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:12">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>399</v>
       </c>
@@ -17998,7 +18014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:12">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>400</v>
       </c>
@@ -18033,7 +18049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="403" spans="1:12">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>401</v>
       </c>
@@ -18071,7 +18087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="1:12">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>402</v>
       </c>
@@ -18109,7 +18125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:12">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>403</v>
       </c>
@@ -18147,7 +18163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:12">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>404</v>
       </c>
@@ -18185,7 +18201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:12">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>405</v>
       </c>
@@ -18223,7 +18239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="408" spans="1:12">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>406</v>
       </c>
@@ -18261,7 +18277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:12">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>407</v>
       </c>
@@ -18299,7 +18315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" spans="1:12">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>408</v>
       </c>
@@ -18337,7 +18353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:12">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>409</v>
       </c>
@@ -18375,7 +18391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:12">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>410</v>
       </c>
@@ -18413,7 +18429,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:12">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>411</v>
       </c>
@@ -18451,7 +18467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:12">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>412</v>
       </c>
@@ -18489,7 +18505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:12">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>413</v>
       </c>
@@ -18527,7 +18543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:12">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>414</v>
       </c>
@@ -18565,7 +18581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:12">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>415</v>
       </c>
@@ -18603,7 +18619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:12">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>416</v>
       </c>
@@ -18638,7 +18654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:12">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>417</v>
       </c>
@@ -18676,7 +18692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:12">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>418</v>
       </c>
@@ -18711,7 +18727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:12">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>419</v>
       </c>
@@ -18749,7 +18765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="422" spans="1:12">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>420</v>
       </c>
@@ -18787,7 +18803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="423" spans="1:12">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>421</v>
       </c>
@@ -18825,7 +18841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:12">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>422</v>
       </c>
@@ -18863,7 +18879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:12">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>423</v>
       </c>
@@ -18901,7 +18917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:12">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>424</v>
       </c>
@@ -18939,7 +18955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:12">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>425</v>
       </c>
@@ -18977,7 +18993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:12">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>426</v>
       </c>
@@ -19015,7 +19031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:12">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>427</v>
       </c>
@@ -19053,7 +19069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:12">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>428</v>
       </c>
@@ -19091,7 +19107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:12">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>429</v>
       </c>
@@ -19129,7 +19145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="432" spans="1:12">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>430</v>
       </c>
@@ -19167,7 +19183,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="433" spans="1:12">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>431</v>
       </c>
@@ -19205,7 +19221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:12">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>432</v>
       </c>
@@ -19243,7 +19259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:12">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>433</v>
       </c>
@@ -19281,7 +19297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:12">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>434</v>
       </c>
@@ -19319,7 +19335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="437" spans="1:12">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>435</v>
       </c>
@@ -19357,7 +19373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="438" spans="1:12">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>436</v>
       </c>
@@ -19395,7 +19411,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="439" spans="1:12">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>437</v>
       </c>
@@ -19433,7 +19449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="440" spans="1:12">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>438</v>
       </c>
@@ -19471,7 +19487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="441" spans="1:12">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>439</v>
       </c>
@@ -19509,7 +19525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:12">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>440</v>
       </c>
@@ -19547,7 +19563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="443" spans="1:12">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>441</v>
       </c>
@@ -19582,7 +19598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:12">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>442</v>
       </c>
@@ -19620,7 +19636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:12">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>443</v>
       </c>
@@ -19655,7 +19671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:12">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>444</v>
       </c>
@@ -19690,7 +19706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="447" spans="1:12">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>445</v>
       </c>
@@ -19728,7 +19744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="448" spans="1:12">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>446</v>
       </c>
@@ -19766,7 +19782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="449" spans="1:12">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>447</v>
       </c>
@@ -19804,7 +19820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="450" spans="1:12">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>448</v>
       </c>
@@ -19842,7 +19858,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="451" spans="1:12">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>449</v>
       </c>
@@ -19880,7 +19896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="452" spans="1:12">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>450</v>
       </c>
@@ -19918,7 +19934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="453" spans="1:12">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>451</v>
       </c>
@@ -19956,7 +19972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:12">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>452</v>
       </c>
@@ -19994,7 +20010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="455" spans="1:12">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>453</v>
       </c>
@@ -20032,7 +20048,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="456" spans="1:12">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>454</v>
       </c>
@@ -20070,7 +20086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:12">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>455</v>
       </c>
@@ -20108,7 +20124,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="458" spans="1:12">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>456</v>
       </c>
@@ -20146,7 +20162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="459" spans="1:12">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>457</v>
       </c>
@@ -20184,7 +20200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:12">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>458</v>
       </c>
@@ -20222,7 +20238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="461" spans="1:12">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>459</v>
       </c>
@@ -20260,7 +20276,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="462" spans="1:12">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>460</v>
       </c>
@@ -20298,7 +20314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="463" spans="1:12">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>461</v>
       </c>
@@ -20336,7 +20352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="464" spans="1:12">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>462</v>
       </c>
@@ -20374,7 +20390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:12">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>463</v>
       </c>
@@ -20412,7 +20428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:12">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>464</v>
       </c>
@@ -20450,7 +20466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="467" spans="1:12">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>465</v>
       </c>
@@ -20485,7 +20501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:12">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>466</v>
       </c>
@@ -20520,7 +20536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="469" spans="1:12">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>467</v>
       </c>
@@ -20558,7 +20574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:12">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>468</v>
       </c>
@@ -20596,7 +20612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:12">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>469</v>
       </c>
@@ -20634,7 +20650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="472" spans="1:12">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>470</v>
       </c>
@@ -20672,7 +20688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="473" spans="1:12">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>471</v>
       </c>
@@ -20710,7 +20726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:12">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>472</v>
       </c>
@@ -20748,7 +20764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="475" spans="1:12">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>473</v>
       </c>
@@ -20786,7 +20802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:12">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>474</v>
       </c>
@@ -20824,7 +20840,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="477" spans="1:12">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>475</v>
       </c>
@@ -20862,7 +20878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:12">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>476</v>
       </c>
@@ -20900,7 +20916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:12">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>477</v>
       </c>
@@ -20935,7 +20951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:12">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>478</v>
       </c>
@@ -20973,7 +20989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:12">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>479</v>
       </c>
@@ -21008,7 +21024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:12">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>480</v>
       </c>
@@ -21043,7 +21059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:12">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>481</v>
       </c>
@@ -21078,7 +21094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:12">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>482</v>
       </c>
@@ -21116,7 +21132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="485" spans="1:12">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>483</v>
       </c>
@@ -21154,7 +21170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:12">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>484</v>
       </c>
@@ -21192,7 +21208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:12">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>485</v>
       </c>
@@ -21230,7 +21246,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="488" spans="1:12">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>486</v>
       </c>
@@ -21265,7 +21281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:12">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>487</v>
       </c>
@@ -21303,7 +21319,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="490" spans="1:12">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>488</v>
       </c>
@@ -21338,7 +21354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:12">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>489</v>
       </c>
@@ -21373,7 +21389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:12">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>490</v>
       </c>
@@ -21411,7 +21427,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="493" spans="1:12">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>491</v>
       </c>
@@ -21449,7 +21465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="494" spans="1:12">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>492</v>
       </c>
@@ -21487,7 +21503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="495" spans="1:12">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>493</v>
       </c>
@@ -21525,7 +21541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="496" spans="1:12">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>494</v>
       </c>
@@ -21563,7 +21579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="497" spans="1:12">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>495</v>
       </c>
@@ -21601,7 +21617,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="498" spans="1:12">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>496</v>
       </c>
@@ -21636,7 +21652,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="499" spans="1:12">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>497</v>
       </c>
@@ -21674,7 +21690,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="500" spans="1:12">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>498</v>
       </c>
@@ -21712,7 +21728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:12">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>499</v>
       </c>
@@ -21750,7 +21766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:12">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>500</v>
       </c>
@@ -21785,7 +21801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:12">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>501</v>
       </c>
@@ -21820,7 +21836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:12">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>502</v>
       </c>
@@ -21855,7 +21871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="505" spans="1:12">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>503</v>
       </c>
@@ -21893,7 +21909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:12">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>504</v>
       </c>
@@ -21931,7 +21947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="507" spans="1:12">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>505</v>
       </c>
@@ -21969,7 +21985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="508" spans="1:12">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>506</v>
       </c>
@@ -22007,7 +22023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="509" spans="1:12">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>507</v>
       </c>
@@ -22045,7 +22061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:12">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>508</v>
       </c>
@@ -22083,7 +22099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="511" spans="1:12">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>509</v>
       </c>
@@ -22121,7 +22137,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="512" spans="1:12">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>510</v>
       </c>
@@ -22156,7 +22172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:12">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>511</v>
       </c>
@@ -22191,7 +22207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="514" spans="1:12">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>512</v>
       </c>
@@ -22226,7 +22242,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="515" spans="1:12">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>513</v>
       </c>
@@ -22264,7 +22280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="516" spans="1:12">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>514</v>
       </c>
@@ -22299,7 +22315,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="517" spans="1:12">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>515</v>
       </c>
@@ -22337,7 +22353,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="518" spans="1:12">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>516</v>
       </c>
@@ -22372,7 +22388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:12">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>517</v>
       </c>
@@ -22407,7 +22423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:12">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>518</v>
       </c>
@@ -22442,7 +22458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:12">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>519</v>
       </c>
@@ -22480,7 +22496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="522" spans="1:12">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>520</v>
       </c>
@@ -22518,7 +22534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="523" spans="1:12">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>521</v>
       </c>
@@ -22556,7 +22572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:12">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>522</v>
       </c>
@@ -22594,7 +22610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="525" spans="1:12">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>523</v>
       </c>
@@ -22632,7 +22648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="526" spans="1:12">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>524</v>
       </c>
@@ -22670,7 +22686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="527" spans="1:12">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>525</v>
       </c>
@@ -22708,7 +22724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:12">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>526</v>
       </c>
@@ -22746,7 +22762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="529" spans="1:12">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>527</v>
       </c>
@@ -22784,7 +22800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:12">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>528</v>
       </c>
@@ -22822,7 +22838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:12">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>529</v>
       </c>
@@ -22860,7 +22876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:12">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>530</v>
       </c>
@@ -22898,7 +22914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:12">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>531</v>
       </c>
@@ -22936,7 +22952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="534" spans="1:12">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>532</v>
       </c>
@@ -22974,7 +22990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:12">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>533</v>
       </c>
@@ -23012,7 +23028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:12">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>534</v>
       </c>
@@ -23050,7 +23066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:12">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>535</v>
       </c>
@@ -23088,7 +23104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:12">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>536</v>
       </c>
@@ -23123,7 +23139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:12">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>537</v>
       </c>
@@ -23161,7 +23177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="540" spans="1:12">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>538</v>
       </c>
